--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-la-araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-la-araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2387-364-CM26</t>
+          <t>707423-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>72037.42999999999</v>
+        <v>24518.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4118-31-CM26</t>
+          <t>1658-1959-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>27195.83</v>
+        <v>24532.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4118-32-CM26</t>
+          <t>2387-119-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>59679.82</v>
+        <v>80167.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4177-100-CM26</t>
+          <t>4050-155-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25368.27</v>
+        <v>32339.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4125-110-CM26</t>
+          <t>3608-159-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>38588.16</v>
+        <v>43574.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3887-303-CM26</t>
+          <t>1426099-58-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,1901 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>29558.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1426099-66-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>25556.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1207-1-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>35109.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3836-293-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.191.400-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Tolten</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>DERCOMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.545.450-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>179118.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3935-68-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>27447.51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4050-266-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.181.100-k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>49766.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4513-54-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.180.400-3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>36123.63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3516-347-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.190.500-4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>18451.67</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4170-134-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>69847.46000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4179-1300-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>36584.74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2389-300-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>36697.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2546-454-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>19700.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3587-148-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.190.500-4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>36781.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3937-205-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.252.400-4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>35533.19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2546-641-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>25288.98</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1685-88-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>29185.39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1685-89-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>33854.64</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2389-514-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>33435.92</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3477-493-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>39448.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3495-176-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>34680.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4513-112-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.180.400-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>84008.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>722-172-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>72.201.100-7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>51382.32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1658-4733-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>22931.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>655-2287-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.821.000-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>51992.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1148-105-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>26801.81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3434-115-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>24601.88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2387-364-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>72037.42999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4118-31-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>27195.83</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4118-32-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>59679.82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4177-100-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>25368.27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4125-110-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>70.766.500-9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>38588.16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3887-303-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>25838.53</v>
       </c>
     </row>
